--- a/data/extracted/inventory-receipts/CONTENEDOR PERUANA 310 13 MARZO.XLSX
+++ b/data/extracted/inventory-receipts/CONTENEDOR PERUANA 310 13 MARZO.XLSX
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363D51D2-E689-4E4B-9608-3E6882F54503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2509,9 +2511,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="###,###,###,###,##0.#0"/>
+    <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -2552,23 +2554,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2768,7 +2764,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -2777,7 +2773,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -3058,18 +3054,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L540"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -3078,7 +3074,7 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3086,10 +3082,10 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -22716,4 +22712,19 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{158355DA-7A0F-4122-937A-A8F3B0D655A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1">
+        <v>47874</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>